--- a/spacecraft.xlsx
+++ b/spacecraft.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Spacecraft" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="How to" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Payloads" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="How to" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -554,8 +555,8 @@
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Epoch" prompt="UTC, at or before the window start (an hour before the run). E.g. 01 Oct 2026 00:00:00 or a date-time cell."/>
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="SMA" prompt="Semi-major axis, km, about the body (Moon radius 1737.4 km, Earth 6378.1 km)."/>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ECC" prompt="Eccentricity, 0 to below 1."/>
-    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="INC" prompt="Inclination, deg, to the body's MJ2000 equator (EarthMJ2000Eq axes)."/>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="RAAN" prompt="Right ascension of the ascending node, deg (MJ2000Eq axes)."/>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="INC" prompt="Inclination, deg. Earth: to the EarthMJ2000Eq equator. Moon: to the Moon's equator of date (90 = polar)."/>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="RAAN" prompt="RAAN, deg. Earth: EarthMJ2000Eq. Moon: from the node of the lunar equator on the Earth's J2000 equator."/>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="AOP" prompt="Argument of periapsis, deg."/>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="TA" prompt="True anomaly at Epoch, deg."/>
     <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="OEM file" prompt="Source = OEM: the CCSDS OEM file, absolute or relative to the project folder."/>
@@ -576,7 +577,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Spacecraft</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tx power (W)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Antenna gain (dBi)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Downlink rate (bps)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Required Eb/N0 (dB)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Rx G/T (dB/K)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Uplink rate (bps)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Other losses (dB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Example lunar orbiter</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>64000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="8">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Spacecraft" prompt="Its name (as in the Spacecraft sheet or the TLE's name line) or catalog number."/>
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Transmit power" prompt="Downlink transmitter power, watts."/>
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Antenna gain" prompt="The spacecraft antenna's gain toward the station, dBi (patch ~6, high-gain dish ~30)."/>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Downlink data rate" prompt="Bits per second, e.g. 64000."/>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Required Eb/N0" prompt="For the modulation and coding used (e.g. ~2.5 dB turbo-coded, ~9.6 dB uncoded BPSK at 1e-5)."/>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Receive G/T" prompt="The spacecraft receiver's G/T for the uplink, dB/K (e.g. -25)."/>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Uplink data rate" prompt="Bits per second, e.g. 2000. Used with 2-way stations."/>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Other losses" prompt="Pointing, polarisation, atmosphere and implementation losses, dB (blank = 0)."/>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -636,14 +741,14 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Elements: Epoch (UTC) and osculating SMA, ECC, INC, RAAN, AOP, TA about Body, in Body-centred axes parallel</t>
+          <t>Elements: Epoch (UTC) and osculating SMA, ECC, INC, RAAN, AOP, TA about Body. Earth: EarthMJ2000Eq axes.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    to EarthMJ2000Eq (GMAT MJ2000Eq). The Epoch must be at or before the window start (an hour before the run).</t>
+          <t xml:space="preserve">    Moon: the Moon's equator of date at the Epoch (so INC 90 is polar). The Epoch must be at or before the window start (an hour before the run).</t>
         </is>
       </c>
     </row>
@@ -699,6 +804,30 @@
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Check the sheet on its own with  python tools\spacecraft.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Payloads sheet - each spacecraft's radio for link budgets, one row per spacecraft, by name or catalog</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    number (TLE spacecraft too). Downlink: Tx power, antenna gain, rate, required Eb/N0. Uplink (2-way</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    stations): Rx G/T and uplink rate. The example row's values are illustrative.</t>
         </is>
       </c>
     </row>

--- a/spacecraft.xlsx
+++ b/spacecraft.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Spacecraft" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Payloads" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Radios" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="How to" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -577,20 +577,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Spacecraft</t>
@@ -598,35 +601,50 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Radio</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Downlink (MHz)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Uplink (MHz)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Tx power (W)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Antenna gain (dBi)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Downlink rate (bps)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Required Eb/N0 (dB)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Rx G/T (dB/K)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Uplink rate (bps)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Other losses (dB)</t>
         </is>
@@ -638,39 +656,70 @@
           <t>Example lunar orbiter</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S-band TT&amp;C</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="C2" t="n">
+      <c r="F2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" t="n">
         <v>64000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>-25</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>2000</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Example lunar orbiter</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>X-band science</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8450</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="8">
-    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Spacecraft" prompt="Its name (as in the Spacecraft sheet or the TLE's name line) or catalog number."/>
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Transmit power" prompt="Downlink transmitter power, watts."/>
-    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Antenna gain" prompt="The spacecraft antenna's gain toward the station, dBi (patch ~6, high-gain dish ~30)."/>
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Downlink data rate" prompt="Bits per second, e.g. 64000."/>
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Required Eb/N0" prompt="For the modulation and coding used (e.g. ~2.5 dB turbo-coded, ~9.6 dB uncoded BPSK at 1e-5)."/>
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Receive G/T" prompt="The spacecraft receiver's G/T for the uplink, dB/K (e.g. -25)."/>
-    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Uplink data rate" prompt="Bits per second, e.g. 2000. Used with 2-way stations."/>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Other losses" prompt="Pointing, polarisation, atmosphere and implementation losses, dB (blank = 0)."/>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -681,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -808,26 +857,58 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Radios sheet - the spacecraft's radios for link budgets, one row per radio: as many per spacecraft as it</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Payloads sheet - each spacecraft's radio for link budgets, one row per spacecraft, by name or catalog</t>
+          <t xml:space="preserve">    carries (S-band TT&amp;C, X-band science, Ka-band ...). Spacecraft: its name or catalog number (TLE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    number (TLE spacecraft too). Downlink: Tx power, antenna gain, rate, required Eb/N0. Uplink (2-way</t>
+          <t xml:space="preserve">    spacecraft too). Radio: a name (blank = its band).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    stations): Rx G/T and uplink rate. The example row's values are illustrative.</t>
+          <t xml:space="preserve">    Downlink (MHz) - needed: sets the band (S 2-4 GHz, C 4-8, X 8-12, Ku 12-18, K 18-27, Ka 27-40). The radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    works with every ground-station radio in the same band (groundstations, sheet Station radios).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Uplink (MHz) - what it receives on a 2-way link; blank = the station's uplink frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Downlink budget: Tx power, antenna gain, rate, required Eb/N0. Uplink: Rx G/T and uplink rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Other losses: pointing, polarisation, atmosphere, implementation. The example values are illustrative.</t>
         </is>
       </c>
     </row>
